--- a/sources/wang_step10.xlsx
+++ b/sources/wang_step10.xlsx
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist Uppercut [Tag]</t>
+          <t>G-Clef - Club Fist Uppercut</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>G-Clef - Club Fist Uppercut [Tag]</t>
+          <t>G-Clef - Club Fist Uppercut</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3799,6 +3799,11 @@
       <c r="X41" t="inlineStr">
         <is>
           <t>JG</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>TRUE</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">

--- a/sources/wang_step10.xlsx
+++ b/sources/wang_step10.xlsx
@@ -960,6 +960,11 @@
           <t>Crouch</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
+        </is>
+      </c>
       <c r="AB7" t="inlineStr">
         <is>
           <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
@@ -1027,6 +1032,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
+        </is>
+      </c>
       <c r="AB8" t="inlineStr">
         <is>
           <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
@@ -1099,6 +1109,11 @@
           <t>TRUE</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
+        </is>
+      </c>
       <c r="AB9" t="inlineStr">
         <is>
           <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
@@ -1164,6 +1179,11 @@
       <c r="W10" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0bbb7217-3bd9-4aa5-bd95-cfe77d966840</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -7572,6 +7592,11 @@
       <c r="U81" t="inlineStr">
         <is>
           <t>hmmhlmhhLm</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>f2b1b105-8e73-4505-9cf6-fc48f600c675</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">

--- a/sources/wang_step10.xlsx
+++ b/sources/wang_step10.xlsx
@@ -417,39 +417,40 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD81"/>
+  <dimension ref="A1:AE81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
     <col hidden="1" min="2" max="2"/>
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
-    <col hidden="1" min="5" max="5"/>
-    <col width="46" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
-    <col hidden="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
-    <col hidden="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col hidden="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col hidden="1" min="15" max="15"/>
-    <col width="22" customWidth="1" min="16" max="16"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col hidden="1" min="6" max="6"/>
+    <col width="46" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
+    <col hidden="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col hidden="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col hidden="1" min="14" max="14"/>
+    <col width="14" customWidth="1" min="15" max="15"/>
+    <col hidden="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
-    <col hidden="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
-    <col hidden="1" min="20" max="20"/>
-    <col width="16" customWidth="1" min="21" max="21"/>
-    <col width="12" customWidth="1" min="22" max="22"/>
-    <col width="14" customWidth="1" min="23" max="23"/>
-    <col width="12" customWidth="1" min="24" max="24"/>
-    <col width="72" customWidth="1" min="25" max="25"/>
-    <col width="10" customWidth="1" min="26" max="26"/>
-    <col width="38" customWidth="1" min="27" max="27"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+    <col hidden="1" min="19" max="19"/>
+    <col width="22" customWidth="1" min="20" max="20"/>
+    <col hidden="1" min="21" max="21"/>
+    <col width="16" customWidth="1" min="22" max="22"/>
+    <col width="12" customWidth="1" min="23" max="23"/>
+    <col width="14" customWidth="1" min="24" max="24"/>
+    <col width="12" customWidth="1" min="25" max="25"/>
+    <col width="72" customWidth="1" min="26" max="26"/>
+    <col width="10" customWidth="1" min="27" max="27"/>
     <col width="38" customWidth="1" min="28" max="28"/>
     <col width="38" customWidth="1" min="29" max="29"/>
-    <col width="11" customWidth="1" min="30" max="30"/>
+    <col width="38" customWidth="1" min="30" max="30"/>
+    <col width="11" customWidth="1" min="31" max="31"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -482,130 +483,135 @@
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F2" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F2" s="1" t="inlineStr">
+      <c r="G2" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G2" s="1" t="inlineStr">
+      <c r="H2" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H2" s="1" t="inlineStr">
+      <c r="I2" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I2" s="1" t="inlineStr">
+      <c r="J2" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J2" s="1" t="inlineStr">
+      <c r="K2" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K2" s="1" t="inlineStr">
+      <c r="L2" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L2" s="1" t="inlineStr">
+      <c r="M2" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M2" s="1" t="inlineStr">
+      <c r="N2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N2" s="1" t="inlineStr">
+      <c r="O2" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O2" s="1" t="inlineStr">
+      <c r="P2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P2" s="1" t="inlineStr">
+      <c r="Q2" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q2" s="1" t="inlineStr">
+      <c r="R2" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R2" s="1" t="inlineStr">
+      <c r="S2" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S2" s="1" t="inlineStr">
+      <c r="T2" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T2" s="1" t="inlineStr">
+      <c r="U2" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U2" s="1" t="inlineStr">
+      <c r="V2" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V2" s="1" t="inlineStr">
+      <c r="W2" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W2" s="1" t="inlineStr">
+      <c r="X2" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X2" s="1" t="inlineStr">
+      <c r="Y2" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y2" s="1" t="inlineStr">
+      <c r="Z2" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z2" s="1" t="inlineStr">
+      <c r="AA2" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA2" s="1" t="inlineStr">
+      <c r="AB2" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB2" s="1" t="inlineStr">
+      <c r="AC2" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC2" s="1" t="inlineStr">
+      <c r="AD2" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD2" s="1" t="inlineStr">
+      <c r="AE2" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -622,62 +628,62 @@
           <t>1+3</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Headlock Toss</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>Headlock Toss</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="X3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AB3" t="inlineStr">
         <is>
           <t>6d84b9db-0f3b-46b1-bac1-0fff91f9ad4d</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
         <is>
           <t>cd6e7f5e-d94f-478e-8826-e3bd36c64c4c</t>
         </is>
@@ -694,62 +700,62 @@
           <t>2+4</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Body Slam</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>Body Slam</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AB4" t="inlineStr">
         <is>
           <t>89298f4e-82e9-4008-bf8d-6e0544ada3dd</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AC4" t="inlineStr">
         <is>
           <t>f6303515-95c6-4345-b6ea-3f70d92ffe66</t>
         </is>
@@ -766,67 +772,67 @@
           <t>df+1+3+4</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Dragon Thrust</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>Dragon Thrust</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="W5" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
+      <c r="X5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="Y5" t="inlineStr">
+      <c r="Z5" t="inlineStr">
         <is>
           <t>There is no escape, but the throw attempt can be blocked as a mid hit.</t>
         </is>
       </c>
-      <c r="AA5" t="inlineStr">
+      <c r="AB5" t="inlineStr">
         <is>
           <t>15f91e2d-5394-48b2-8689-6b4328731735</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
+      <c r="AC5" t="inlineStr">
         <is>
           <t>ef00d328-e699-40f0-92d4-ec63f3c19daa</t>
         </is>
@@ -843,67 +849,67 @@
           <t>df,DF+2+4</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Waning Moon</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>Waning Moon</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
+      <c r="W6" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
+      <c r="X6" t="inlineStr">
         <is>
           <t>1+2</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA6" t="inlineStr">
+      <c r="AB6" t="inlineStr">
         <is>
           <t>8c572288-684d-4fdd-b032-811568fd1aec</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AC6" t="inlineStr">
         <is>
           <t>21600fd2-064c-44b6-a8a4-356396f2de48</t>
         </is>
@@ -920,57 +926,57 @@
           <t>b+2 ,1+2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Arm Whip - German Suplex</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>Arm Whip - German Suplex</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>12,45</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>57</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>12,45</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
+      <c r="W7" t="inlineStr">
         <is>
           <t>Front</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
+      <c r="X7" t="inlineStr">
         <is>
           <t>Crouch</t>
         </is>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
         <is>
           <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
+      <c r="AC7" t="inlineStr">
         <is>
           <t>69bbb246-8bd8-4be1-a2c2-f1113edf6288</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -994,55 +1000,60 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
           <t>Crushing Dragon</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>Crushing Dragon</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="I8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
+      <c r="W8" t="inlineStr">
         <is>
           <t>Left</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
+      <c r="X8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
+      <c r="AB8" t="inlineStr">
         <is>
           <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
+      <c r="AC8" t="inlineStr">
         <is>
           <t>b024eb39-fb8b-4f12-9207-4c48609e7fc8</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1066,60 +1077,65 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
           <t>Golden Mountain</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>Golden Mountain</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>40</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="W9" t="inlineStr">
         <is>
           <t>Right</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
+      <c r="X9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
+      <c r="AA9" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA9" t="inlineStr">
+      <c r="AB9" t="inlineStr">
         <is>
           <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
+      <c r="AC9" t="inlineStr">
         <is>
           <t>aeec6651-ae98-4599-8ef6-d5adca58c3cd</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1143,55 +1159,60 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
+          <t>2+4; 2+5</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>Reverse Nech Toss</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>Reverse Nech Toss</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="I10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="V10" t="inlineStr">
+      <c r="W10" t="inlineStr">
         <is>
           <t>Back</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
+      <c r="X10" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="AA10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
         <is>
           <t>0bbb7217-3bd9-4aa5-bd95-cfe77d966840</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
+      <c r="AC10" t="inlineStr">
         <is>
           <t>0bbb7217-3bd9-4aa5-bd95-cfe77d966840</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
@@ -1228,130 +1249,135 @@
       </c>
       <c r="E13" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F13" s="1" t="inlineStr">
+      <c r="G13" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G13" s="1" t="inlineStr">
+      <c r="H13" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H13" s="1" t="inlineStr">
+      <c r="I13" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I13" s="1" t="inlineStr">
+      <c r="J13" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr">
+      <c r="K13" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="L13" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L13" s="1" t="inlineStr">
+      <c r="M13" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M13" s="1" t="inlineStr">
+      <c r="N13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N13" s="1" t="inlineStr">
+      <c r="O13" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O13" s="1" t="inlineStr">
+      <c r="P13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P13" s="1" t="inlineStr">
+      <c r="Q13" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q13" s="1" t="inlineStr">
+      <c r="R13" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R13" s="1" t="inlineStr">
+      <c r="S13" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S13" s="1" t="inlineStr">
+      <c r="T13" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T13" s="1" t="inlineStr">
+      <c r="U13" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U13" s="1" t="inlineStr">
+      <c r="V13" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V13" s="1" t="inlineStr">
+      <c r="W13" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W13" s="1" t="inlineStr">
+      <c r="X13" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X13" s="1" t="inlineStr">
+      <c r="Y13" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y13" s="1" t="inlineStr">
+      <c r="Z13" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z13" s="1" t="inlineStr">
+      <c r="AA13" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA13" s="1" t="inlineStr">
+      <c r="AB13" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB13" s="1" t="inlineStr">
+      <c r="AC13" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC13" s="1" t="inlineStr">
+      <c r="AD13" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD13" s="1" t="inlineStr">
+      <c r="AE13" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -1368,82 +1394,82 @@
           <t>1</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="K14" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr">
+      <c r="N14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
+      <c r="O14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr">
+      <c r="P14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
+      <c r="R14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R14" t="inlineStr">
+      <c r="S14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr">
+      <c r="T14" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr">
+      <c r="U14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr">
+      <c r="V14" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>9e7f8c6d-21d0-4a2d-a184-f806bc0160bc</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>e6eb8679-92dd-428a-95ea-eaea84b13c49</t>
         </is>
@@ -1460,82 +1486,82 @@
           <t>2</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N15" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr">
+      <c r="R15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="S15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr">
+      <c r="T15" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr">
+      <c r="U15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr">
+      <c r="AB15" t="inlineStr">
         <is>
           <t>8123e159-e075-433b-8f4a-08040a726a00</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
+      <c r="AC15" t="inlineStr">
         <is>
           <t>4a9a338a-db9b-41a2-a067-ae06cebed14a</t>
         </is>
@@ -1552,82 +1578,82 @@
           <t>3</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="K16" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr">
+      <c r="R16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="S16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr">
+      <c r="T16" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr">
+      <c r="U16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AB16" t="inlineStr">
         <is>
           <t>e7cfe0bd-cd2b-4663-95e8-58ad222b296b</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AC16" t="inlineStr">
         <is>
           <t>e9790248-e7f8-482a-909f-7870ea5b3732</t>
         </is>
@@ -1644,82 +1670,82 @@
           <t>4</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="K17" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N17" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+      <c r="R17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="S17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr">
+      <c r="T17" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr">
+      <c r="U17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AB17" t="inlineStr">
         <is>
           <t>fe6bb5c3-8226-48cd-9b32-e61b90875b02</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AC17" t="inlineStr">
         <is>
           <t>ddf5705b-df0b-4e8f-a801-4f5af331cc92</t>
         </is>
@@ -1736,82 +1762,82 @@
           <t>f+1</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="K18" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr">
+      <c r="Q18" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr">
+      <c r="R18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R18" t="inlineStr">
+      <c r="S18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr">
+      <c r="T18" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr">
+      <c r="U18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AB18" t="inlineStr">
         <is>
           <t>ee6808e3-1c23-4f68-b869-213455d212d7</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AC18" t="inlineStr">
         <is>
           <t>913468a8-afa8-411c-ac3c-a41a37ccd3e5</t>
         </is>
@@ -1828,82 +1854,82 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr">
+      <c r="R19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="S19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr">
+      <c r="T19" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr">
+      <c r="U19" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr">
+      <c r="V19" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA19" t="inlineStr">
+      <c r="AB19" t="inlineStr">
         <is>
           <t>e707b7f4-3948-4f98-a5a1-5ba74b8aab1d</t>
         </is>
       </c>
-      <c r="AB19" t="inlineStr">
+      <c r="AC19" t="inlineStr">
         <is>
           <t>abd3cd6b-e203-4edb-a322-480e229e96fc</t>
         </is>
@@ -1920,82 +1946,82 @@
           <t>f+3</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="K20" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N20" t="inlineStr">
+      <c r="O20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O20" t="inlineStr">
+      <c r="P20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr">
+      <c r="R20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="S20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr">
+      <c r="T20" t="inlineStr">
         <is>
           <t>25</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr">
+      <c r="U20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA20" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>b05d277b-8a5e-4f13-893f-eb32131f088f</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>29aab8c8-0383-4880-a12f-b16433459004</t>
         </is>
@@ -2012,82 +2038,82 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N21" t="inlineStr">
+      <c r="O21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O21" t="inlineStr">
+      <c r="P21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr">
+      <c r="R21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="S21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr">
+      <c r="T21" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr">
+      <c r="U21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr">
+      <c r="V21" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA21" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>331417a1-b712-4e84-a95a-bd2524abd821</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>9aca19d7-1966-4937-b645-ecaf6661a32e</t>
         </is>
@@ -2104,82 +2130,82 @@
           <t>d+1</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr">
+      <c r="N22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
+      <c r="O22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O22" t="inlineStr">
+      <c r="P22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
+      <c r="R22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="S22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr">
+      <c r="T22" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr">
+      <c r="U22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA22" t="inlineStr">
+      <c r="AB22" t="inlineStr">
         <is>
           <t>712038e1-0276-4eb9-94f3-6bb994c01a88</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
+      <c r="AC22" t="inlineStr">
         <is>
           <t>eb8bceae-0701-485e-83fe-858d3fbd69a2</t>
         </is>
@@ -2196,82 +2222,82 @@
           <t>d+2</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="K23" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
+      <c r="O23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O23" t="inlineStr">
+      <c r="P23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr">
+      <c r="R23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="S23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr">
+      <c r="T23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr">
+      <c r="U23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr">
+      <c r="V23" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA23" t="inlineStr">
+      <c r="AB23" t="inlineStr">
         <is>
           <t>c65163ad-b4a2-4255-97cc-4e5ee881aa09</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
+      <c r="AC23" t="inlineStr">
         <is>
           <t>118f234b-c6cd-4c40-a3f0-a1871e7c0ef6</t>
         </is>
@@ -2288,82 +2314,82 @@
           <t>d+3</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="K24" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
+      <c r="O24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O24" t="inlineStr">
+      <c r="P24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr">
+      <c r="R24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="S24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr">
+      <c r="T24" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr">
+      <c r="U24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr">
+      <c r="V24" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA24" t="inlineStr">
+      <c r="AB24" t="inlineStr">
         <is>
           <t>1d75587b-d22f-4f33-9470-8ef09c8d4969</t>
         </is>
       </c>
-      <c r="AB24" t="inlineStr">
+      <c r="AC24" t="inlineStr">
         <is>
           <t>f5fea6cb-e96b-4ba9-bd57-56af139a12af</t>
         </is>
@@ -2380,82 +2406,82 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="K25" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="N25" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
+      <c r="O25" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="O25" t="inlineStr">
+      <c r="P25" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>+4</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
+      <c r="R25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA25" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>05d848d7-4e57-47ec-9600-90a187a820f7</t>
         </is>
       </c>
-      <c r="AB25" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>26488032-d061-4c2a-9d88-76494ec601d1</t>
         </is>
@@ -2472,82 +2498,82 @@
           <t>FC+1</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="K26" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
+      <c r="O26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O26" t="inlineStr">
+      <c r="P26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q26" t="inlineStr">
+      <c r="R26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="S26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S26" t="inlineStr">
+      <c r="T26" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="U26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA26" t="inlineStr">
+      <c r="AB26" t="inlineStr">
         <is>
           <t>621aa2ba-c042-4b15-85d5-389734da6ebb</t>
         </is>
       </c>
-      <c r="AB26" t="inlineStr">
+      <c r="AC26" t="inlineStr">
         <is>
           <t>ba392683-3801-4b10-bcd8-0a664851f748</t>
         </is>
@@ -2564,82 +2590,82 @@
           <t>FC+2</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="K27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
+      <c r="O27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O27" t="inlineStr">
+      <c r="P27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q27" t="inlineStr">
+      <c r="R27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="S27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="T27" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr">
+      <c r="U27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr">
+      <c r="V27" t="inlineStr">
         <is>
           <t>s</t>
         </is>
       </c>
-      <c r="AA27" t="inlineStr">
+      <c r="AB27" t="inlineStr">
         <is>
           <t>318da901-9558-47f3-9a13-cad95d65a0c2</t>
         </is>
       </c>
-      <c r="AB27" t="inlineStr">
+      <c r="AC27" t="inlineStr">
         <is>
           <t>89137398-4577-47d2-8b2a-ab84f36c1f15</t>
         </is>
@@ -2656,82 +2682,82 @@
           <t>FC+3</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="K28" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N28" t="inlineStr">
+      <c r="O28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="O28" t="inlineStr">
+      <c r="P28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="Q28" t="inlineStr">
+      <c r="R28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="S28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S28" t="inlineStr">
+      <c r="T28" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T28" t="inlineStr">
+      <c r="U28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr">
+      <c r="V28" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA28" t="inlineStr">
+      <c r="AB28" t="inlineStr">
         <is>
           <t>010a54ee-c8da-45d1-b6a5-c463bec3607b</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
+      <c r="AC28" t="inlineStr">
         <is>
           <t>e84a47a8-3c6d-44d7-b817-475bb202ea59</t>
         </is>
@@ -2748,82 +2774,82 @@
           <t>FC+4</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="K29" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N29" t="inlineStr">
+      <c r="O29" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O29" t="inlineStr">
+      <c r="P29" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="Q29" t="inlineStr">
+      <c r="R29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="S29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S29" t="inlineStr">
+      <c r="T29" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T29" t="inlineStr">
+      <c r="U29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>l</t>
         </is>
       </c>
-      <c r="AA29" t="inlineStr">
+      <c r="AB29" t="inlineStr">
         <is>
           <t>623ec7d5-c843-4614-b414-a89c69268088</t>
         </is>
       </c>
-      <c r="AB29" t="inlineStr">
+      <c r="AC29" t="inlineStr">
         <is>
           <t>31649578-9917-4c3e-8d6d-821baf975ca1</t>
         </is>
@@ -2840,82 +2866,82 @@
           <t>WS+1</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="K30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="M30" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr">
+      <c r="N30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="N30" t="inlineStr">
+      <c r="O30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="O30" t="inlineStr">
+      <c r="P30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>+9</t>
         </is>
       </c>
-      <c r="Q30" t="inlineStr">
+      <c r="R30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="S30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr">
+      <c r="T30" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T30" t="inlineStr">
+      <c r="U30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr">
+      <c r="V30" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA30" t="inlineStr">
+      <c r="AB30" t="inlineStr">
         <is>
           <t>15f48a57-9f53-484f-b849-5b08174921b9</t>
         </is>
       </c>
-      <c r="AB30" t="inlineStr">
+      <c r="AC30" t="inlineStr">
         <is>
           <t>20351df2-b208-4ff6-adcd-6f252e236422</t>
         </is>
@@ -2932,82 +2958,82 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="K31" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
+      <c r="O31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
+      <c r="P31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="R31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="S31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr">
+      <c r="T31" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T31" t="inlineStr">
+      <c r="U31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA31" t="inlineStr">
+      <c r="AB31" t="inlineStr">
         <is>
           <t>367df77c-2d55-4de3-9075-550df628b574</t>
         </is>
       </c>
-      <c r="AB31" t="inlineStr">
+      <c r="AC31" t="inlineStr">
         <is>
           <t>e41150f0-80cc-4176-a1bd-69592f82e04b</t>
         </is>
@@ -3024,82 +3050,82 @@
           <t>WS+3</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="K32" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>-16</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N32" t="inlineStr">
+      <c r="O32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
+      <c r="P32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="R32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="S32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S32" t="inlineStr">
+      <c r="T32" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T32" t="inlineStr">
+      <c r="U32" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr">
+      <c r="V32" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="AA32" t="inlineStr">
+      <c r="AB32" t="inlineStr">
         <is>
           <t>d0f8f4ef-2764-4e7f-af4b-d88bd2076fa6</t>
         </is>
       </c>
-      <c r="AB32" t="inlineStr">
+      <c r="AC32" t="inlineStr">
         <is>
           <t>1385532d-1d37-4a47-abe6-011c26848311</t>
         </is>
@@ -3116,82 +3142,82 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="K33" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="O33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
+      <c r="P33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="R33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="S33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S33" t="inlineStr">
+      <c r="T33" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T33" t="inlineStr">
+      <c r="U33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr">
+      <c r="V33" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA33" t="inlineStr">
+      <c r="AB33" t="inlineStr">
         <is>
           <t>f13eb267-b56d-46d8-a671-af17cc438616</t>
         </is>
       </c>
-      <c r="AB33" t="inlineStr">
+      <c r="AC33" t="inlineStr">
         <is>
           <t>0cf29b31-86f5-4da2-8458-5f575f035997</t>
         </is>
@@ -3208,82 +3234,82 @@
           <t>df+1</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>-15</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="N34" t="inlineStr">
+      <c r="O34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
+      <c r="P34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="R34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="S34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S34" t="inlineStr">
+      <c r="T34" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="T34" t="inlineStr">
+      <c r="U34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr">
+      <c r="V34" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA34" t="inlineStr">
+      <c r="AB34" t="inlineStr">
         <is>
           <t>4ad72bc8-5cfd-483f-a128-becab80b455e</t>
         </is>
       </c>
-      <c r="AB34" t="inlineStr">
+      <c r="AC34" t="inlineStr">
         <is>
           <t>0c31184e-3298-44b0-9792-d8ea418f69c4</t>
         </is>
@@ -3300,82 +3326,82 @@
           <t>df+2</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I35" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr">
+      <c r="K35" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>-6</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
+      <c r="O35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
+      <c r="P35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>+5</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="R35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="S35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S35" t="inlineStr">
+      <c r="T35" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T35" t="inlineStr">
+      <c r="U35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr">
+      <c r="V35" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA35" t="inlineStr">
+      <c r="AB35" t="inlineStr">
         <is>
           <t>3879413f-a778-4be2-b613-757b9b74a2da</t>
         </is>
       </c>
-      <c r="AB35" t="inlineStr">
+      <c r="AC35" t="inlineStr">
         <is>
           <t>465a1c45-3294-4d48-9555-5f8ce127e86d</t>
         </is>
@@ -3392,82 +3418,82 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I36" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J36" t="inlineStr">
+      <c r="K36" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N36" t="inlineStr">
+      <c r="O36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O36" t="inlineStr">
+      <c r="P36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
+      <c r="R36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="S36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S36" t="inlineStr">
+      <c r="T36" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T36" t="inlineStr">
+      <c r="U36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr">
+      <c r="V36" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA36" t="inlineStr">
+      <c r="AB36" t="inlineStr">
         <is>
           <t>2482f9cb-b1c6-404f-9c50-42de5b1a3df4</t>
         </is>
       </c>
-      <c r="AB36" t="inlineStr">
+      <c r="AC36" t="inlineStr">
         <is>
           <t>87bda466-8129-4b93-8140-a2bd8fb6d355</t>
         </is>
@@ -3484,82 +3510,82 @@
           <t>df+4</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I37" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr">
+      <c r="K37" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>-4</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="N37" t="inlineStr">
+      <c r="O37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="O37" t="inlineStr">
+      <c r="P37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>+7</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
+      <c r="R37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="S37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr">
+      <c r="T37" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T37" t="inlineStr">
+      <c r="U37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr">
+      <c r="V37" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr">
+      <c r="AB37" t="inlineStr">
         <is>
           <t>0059d0d7-c0e8-4a50-a200-83f8f97d0cd6</t>
         </is>
       </c>
-      <c r="AB37" t="inlineStr">
+      <c r="AC37" t="inlineStr">
         <is>
           <t>eb5a7734-5455-40bf-8b1f-1ebe69a5ba7d</t>
         </is>
@@ -3596,130 +3622,135 @@
       </c>
       <c r="E40" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F40" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F40" s="1" t="inlineStr">
+      <c r="G40" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G40" s="1" t="inlineStr">
+      <c r="H40" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H40" s="1" t="inlineStr">
+      <c r="I40" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I40" s="1" t="inlineStr">
+      <c r="J40" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J40" s="1" t="inlineStr">
+      <c r="K40" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K40" s="1" t="inlineStr">
+      <c r="L40" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L40" s="1" t="inlineStr">
+      <c r="M40" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M40" s="1" t="inlineStr">
+      <c r="N40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N40" s="1" t="inlineStr">
+      <c r="O40" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O40" s="1" t="inlineStr">
+      <c r="P40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P40" s="1" t="inlineStr">
+      <c r="Q40" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q40" s="1" t="inlineStr">
+      <c r="R40" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R40" s="1" t="inlineStr">
+      <c r="S40" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S40" s="1" t="inlineStr">
+      <c r="T40" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T40" s="1" t="inlineStr">
+      <c r="U40" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U40" s="1" t="inlineStr">
+      <c r="V40" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V40" s="1" t="inlineStr">
+      <c r="W40" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W40" s="1" t="inlineStr">
+      <c r="X40" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X40" s="1" t="inlineStr">
+      <c r="Y40" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y40" s="1" t="inlineStr">
+      <c r="Z40" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z40" s="1" t="inlineStr">
+      <c r="AA40" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA40" s="1" t="inlineStr">
+      <c r="AB40" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB40" s="1" t="inlineStr">
+      <c r="AC40" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC40" s="1" t="inlineStr">
+      <c r="AD40" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD40" s="1" t="inlineStr">
+      <c r="AE40" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -3736,102 +3767,102 @@
           <t>1 ~1 ,1</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist Uppercut</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>G-Clef - Club Fist Uppercut</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr">
+      <c r="K41" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>0 -15 -14</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>0 -15 -14</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>+6 +4 KD</t>
         </is>
       </c>
-      <c r="N41" t="inlineStr">
+      <c r="O41" t="inlineStr">
         <is>
           <t>+6 +4 KD</t>
         </is>
       </c>
-      <c r="O41" t="inlineStr">
+      <c r="P41" t="inlineStr">
         <is>
           <t>+6 +4 KD</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>+6 +4 KD</t>
         </is>
       </c>
-      <c r="Q41" t="inlineStr">
+      <c r="R41" t="inlineStr">
         <is>
           <t>10,5,21</t>
         </is>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="S41" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="S41" t="inlineStr">
+      <c r="T41" t="inlineStr">
         <is>
           <t>10,5,21</t>
         </is>
       </c>
-      <c r="T41" t="inlineStr">
+      <c r="U41" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr">
+      <c r="V41" t="inlineStr">
         <is>
           <t>hmm</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
+      <c r="Y41" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
+      <c r="AA41" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA41" t="inlineStr">
+      <c r="AB41" t="inlineStr">
         <is>
           <t>8bb67630-56a3-463d-be98-304a6de9af66</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
+      <c r="AC41" t="inlineStr">
         <is>
           <t>47d5c923-f772-4645-9d5c-83d625074442</t>
         </is>
@@ -3848,102 +3879,102 @@
           <t>df+1 ,1</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>-15 -14</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>-4 D</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
+      <c r="O42" t="inlineStr">
         <is>
           <t>-4 D</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
+      <c r="P42" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>-4 KD</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="R42" t="inlineStr">
         <is>
           <t>8,21</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="S42" t="inlineStr">
         <is>
           <t>29</t>
         </is>
       </c>
-      <c r="S42" t="inlineStr">
+      <c r="T42" t="inlineStr">
         <is>
           <t>8,21</t>
         </is>
       </c>
-      <c r="T42" t="inlineStr">
+      <c r="U42" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr">
+      <c r="V42" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
+      <c r="Y42" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
+      <c r="AA42" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA42" t="inlineStr">
+      <c r="AB42" t="inlineStr">
         <is>
           <t>3bda3345-8c50-4ed0-86d7-82d384cc6faa</t>
         </is>
       </c>
-      <c r="AB42" t="inlineStr">
+      <c r="AC42" t="inlineStr">
         <is>
           <t>491c39a7-6a6f-4376-ab0c-86833caaef26</t>
         </is>
@@ -3967,90 +3998,95 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
+          <t>f,f+1+2; F+1+2</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
           <t>Double Palm Thrust</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>Double Palm Thrust</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr">
+      <c r="I43" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I43" t="inlineStr">
+      <c r="J43" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="K43" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
+      <c r="O43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
+      <c r="P43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="R43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA43" t="inlineStr">
+      <c r="AB43" t="inlineStr">
         <is>
           <t>d65d77cc-f17d-4071-8e4b-26b0748049b5</t>
         </is>
       </c>
-      <c r="AB43" t="inlineStr">
+      <c r="AC43" t="inlineStr">
         <is>
           <t>9b032256-610e-448c-863e-b2b0c4fc0bdc</t>
         </is>
@@ -4067,92 +4103,92 @@
           <t>df+1+2</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>Lunging Double Fist</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>Lunging Double Fist</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
+      <c r="I44" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr">
+      <c r="J44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="J44" t="inlineStr">
+      <c r="K44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
+      <c r="M44" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr">
+      <c r="N44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N44" t="inlineStr">
+      <c r="O44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
+      <c r="P44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="R44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="S44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr">
+      <c r="T44" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="T44" t="inlineStr">
+      <c r="U44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr">
+      <c r="V44" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AA44" t="inlineStr">
+      <c r="AB44" t="inlineStr">
         <is>
           <t>d8f6ee24-1a80-4752-9b05-6494201edb9f</t>
         </is>
       </c>
-      <c r="AB44" t="inlineStr">
+      <c r="AC44" t="inlineStr">
         <is>
           <t>db8193a6-cd30-4739-bdc4-32e3017c8832</t>
         </is>
@@ -4169,97 +4205,97 @@
           <t>1+2</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>Mountain Splitter</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>Mountain Splitter</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
+      <c r="I45" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="N45" t="inlineStr">
+      <c r="O45" t="inlineStr">
         <is>
           <t>-7</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
+      <c r="P45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="R45" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="S45" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr">
+      <c r="T45" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="T45" t="inlineStr">
+      <c r="U45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr">
+      <c r="V45" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
+      <c r="Y45" t="inlineStr">
         <is>
           <t>MS KNDc</t>
         </is>
       </c>
-      <c r="AA45" t="inlineStr">
+      <c r="AB45" t="inlineStr">
         <is>
           <t>2c030b90-8bd8-4692-81d3-37b6d80bdfeb</t>
         </is>
       </c>
-      <c r="AB45" t="inlineStr">
+      <c r="AC45" t="inlineStr">
         <is>
           <t>85e231c9-f388-49a3-8553-4e388067e800</t>
         </is>
@@ -4276,97 +4312,97 @@
           <t>SS+1+2</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>Horse Tamer</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>Horse Tamer</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr">
+      <c r="I46" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="J46" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="K46" t="inlineStr">
         <is>
           <t>19</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>+27</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>+27</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>+15</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
+      <c r="O46" t="inlineStr">
         <is>
           <t>+15</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
+      <c r="P46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="R46" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>22</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
+      <c r="Y46" t="inlineStr">
         <is>
           <t>MS DSc GB</t>
         </is>
       </c>
-      <c r="AA46" t="inlineStr">
+      <c r="AB46" t="inlineStr">
         <is>
           <t>4a7efdc6-9c83-467b-bb63-f2e2da876ac1</t>
         </is>
       </c>
-      <c r="AB46" t="inlineStr">
+      <c r="AC46" t="inlineStr">
         <is>
           <t>fa08c9b9-d23e-4b31-b54b-a69c6a32ef13</t>
         </is>
@@ -4383,92 +4419,92 @@
           <t>qcf+2</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>Power Fist</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>Power Fist</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr">
+      <c r="I47" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I47" t="inlineStr">
+      <c r="J47" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr">
+      <c r="K47" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N47" t="inlineStr">
+      <c r="O47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O47" t="inlineStr">
+      <c r="P47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q47" t="inlineStr">
+      <c r="R47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="S47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr">
+      <c r="T47" t="inlineStr">
         <is>
           <t>30</t>
         </is>
       </c>
-      <c r="T47" t="inlineStr">
+      <c r="U47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr">
+      <c r="V47" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA47" t="inlineStr">
+      <c r="AB47" t="inlineStr">
         <is>
           <t>9333c2b8-2ad6-440c-a7df-08e3ba31c8d4</t>
         </is>
       </c>
-      <c r="AB47" t="inlineStr">
+      <c r="AC47" t="inlineStr">
         <is>
           <t>2798d6b5-799d-4a49-bcdd-638cbab38aa7</t>
         </is>
@@ -4485,107 +4521,107 @@
           <t>df+2 ,1</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>Gut Punch - Skyscraper</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>Gut Punch - Skyscraper</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
+      <c r="I48" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr">
+      <c r="J48" t="inlineStr">
         <is>
           <t>16 x</t>
         </is>
       </c>
-      <c r="J48" t="inlineStr">
+      <c r="K48" t="inlineStr">
         <is>
           <t>16 x</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>-6 x</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
+      <c r="M48" t="inlineStr">
         <is>
           <t>-6 x</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr">
+      <c r="N48" t="inlineStr">
         <is>
           <t>+5 x</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
+      <c r="O48" t="inlineStr">
         <is>
           <t>+5 x</t>
         </is>
       </c>
-      <c r="O48" t="inlineStr">
+      <c r="P48" t="inlineStr">
         <is>
           <t>+5 x</t>
         </is>
       </c>
-      <c r="P48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>+5 x</t>
         </is>
       </c>
-      <c r="Q48" t="inlineStr">
+      <c r="R48" t="inlineStr">
         <is>
           <t>15,21</t>
         </is>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="S48" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="S48" t="inlineStr">
+      <c r="T48" t="inlineStr">
         <is>
           <t>15,21</t>
         </is>
       </c>
-      <c r="T48" t="inlineStr">
+      <c r="U48" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr">
+      <c r="V48" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
+      <c r="Y48" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Y48" t="inlineStr">
+      <c r="Z48" t="inlineStr">
         <is>
           <t>Damage of the1st hit will be 10 if the 2nd isn't executed.</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
+      <c r="AA48" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA48" t="inlineStr">
+      <c r="AB48" t="inlineStr">
         <is>
           <t>5c255c92-a4b1-4575-9150-1858b20437cf</t>
         </is>
       </c>
-      <c r="AB48" t="inlineStr">
+      <c r="AC48" t="inlineStr">
         <is>
           <t>abcbc197-a6be-4da9-88f8-ba89a97b8e40</t>
         </is>
@@ -4602,92 +4638,92 @@
           <t>f+2</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>Front Strike</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>Front Strike</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="I49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
+      <c r="J49" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
+      <c r="K49" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="N49" t="inlineStr">
+      <c r="O49" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="P49" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="P49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>+6</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="S49" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S49" t="inlineStr">
+      <c r="T49" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T49" t="inlineStr">
+      <c r="U49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr">
+      <c r="V49" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA49" t="inlineStr">
+      <c r="AB49" t="inlineStr">
         <is>
           <t>4b61b2c7-1be3-4f04-84cd-d2f7e2983d7c</t>
         </is>
       </c>
-      <c r="AB49" t="inlineStr">
+      <c r="AC49" t="inlineStr">
         <is>
           <t>6d3ef069-0b5f-4dcf-8c6e-9dc052f908d8</t>
         </is>
@@ -4711,95 +4747,100 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>2~b</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>Arm Whip</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
+      <c r="I50" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
+      <c r="J50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J50" t="inlineStr">
+      <c r="K50" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="N50" t="inlineStr">
+      <c r="O50" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="P50" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="R50" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="S50" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="S50" t="inlineStr">
+      <c r="T50" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="T50" t="inlineStr">
+      <c r="U50" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr">
+      <c r="V50" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
+      <c r="Y50" t="inlineStr">
         <is>
           <t>OB</t>
         </is>
       </c>
-      <c r="AA50" t="inlineStr">
+      <c r="AB50" t="inlineStr">
         <is>
           <t>ddc01d8c-269d-4da9-8156-109642197f96</t>
         </is>
       </c>
-      <c r="AB50" t="inlineStr">
+      <c r="AC50" t="inlineStr">
         <is>
           <t>ff017df7-d2c8-4dae-99c8-3f680c954363</t>
         </is>
@@ -4816,77 +4857,77 @@
           <t>b+2 ,1+2</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>– German Suplex</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>Arm Whip – German Suplex</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J51" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>-2</t>
         </is>
       </c>
-      <c r="N51" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="P51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>-1</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="R51" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="S51" t="inlineStr">
         <is>
           <t>45</t>
         </is>
       </c>
-      <c r="S51" t="inlineStr">
+      <c r="T51" t="inlineStr">
         <is>
           <t>12,45</t>
         </is>
       </c>
-      <c r="T51" t="inlineStr">
+      <c r="U51" t="inlineStr">
         <is>
           <t>throw</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr">
+      <c r="V51" t="inlineStr">
         <is>
           <t>hthrow</t>
         </is>
       </c>
-      <c r="AA51" t="inlineStr">
+      <c r="AB51" t="inlineStr">
         <is>
           <t>c6d4b77b-e658-4d9c-b744-4a4666679a82</t>
         </is>
       </c>
-      <c r="AB51" t="inlineStr">
+      <c r="AC51" t="inlineStr">
         <is>
           <t>f9982e6a-de4e-419e-83a2-3e758a6edbe9</t>
         </is>
       </c>
-      <c r="AC51" t="inlineStr">
+      <c r="AD51" t="inlineStr">
         <is>
           <t>ddc01d8c-269d-4da9-8156-109642197f96</t>
         </is>
@@ -4903,92 +4944,92 @@
           <t>WS+2</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>Tequila Sunrise</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>Tequila Sunrise</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="O52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="P52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="R52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA52" t="inlineStr">
+      <c r="AB52" t="inlineStr">
         <is>
           <t>acd6541a-da8f-4664-a6f0-e8e34d017225</t>
         </is>
       </c>
-      <c r="AB52" t="inlineStr">
+      <c r="AC52" t="inlineStr">
         <is>
           <t>e137ef00-3167-46bb-a780-64d3ca5e83dc</t>
         </is>
@@ -5005,107 +5046,107 @@
           <t>WS+2 ,1 ,1</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>– Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>Tequila Sunrise – Club Fist - Flash Uppercut</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J53" t="inlineStr">
+      <c r="K53" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>-14 -14</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>-11 -14 -14</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="N53" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>0 -3 KD</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="P53" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="P53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>0 -3 KD</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="R53" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>31</t>
         </is>
       </c>
-      <c r="S53" t="inlineStr">
+      <c r="T53" t="inlineStr">
         <is>
           <t>15,10,21</t>
         </is>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="U53" t="inlineStr">
         <is>
           <t>mm</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr">
+      <c r="V53" t="inlineStr">
         <is>
           <t>mmm</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
+      <c r="Y53" t="inlineStr">
         <is>
           <t>SH</t>
         </is>
       </c>
-      <c r="Y53" t="inlineStr">
+      <c r="Z53" t="inlineStr">
         <is>
           <t>The uppercut does not juggle, but you can buffer in a tag.</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
+      <c r="AA53" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA53" t="inlineStr">
+      <c r="AB53" t="inlineStr">
         <is>
           <t>f41cf009-aa96-4655-b6b0-9eb88e38769d</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
+      <c r="AC53" t="inlineStr">
         <is>
           <t>f0f18296-2983-47f2-a43b-bbd1bf212b66</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
+      <c r="AD53" t="inlineStr">
         <is>
           <t>acd6541a-da8f-4664-a6f0-e8e34d017225</t>
         </is>
@@ -5122,102 +5163,102 @@
           <t>db+2</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>False Lift</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>False Lift</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="I54" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="J54" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr">
+      <c r="K54" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
+      <c r="M54" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr">
+      <c r="N54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="O54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="P54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q54" t="inlineStr">
+      <c r="R54" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S54" t="inlineStr">
+      <c r="T54" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="U54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr">
+      <c r="V54" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
+      <c r="Y54" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
+      <c r="AA54" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA54" t="inlineStr">
+      <c r="AB54" t="inlineStr">
         <is>
           <t>da058c82-53bb-4381-9acc-bc828293a002</t>
         </is>
       </c>
-      <c r="AB54" t="inlineStr">
+      <c r="AC54" t="inlineStr">
         <is>
           <t>fbaee17c-9f2f-4f5a-a735-79efb328c28c</t>
         </is>
@@ -5234,92 +5275,92 @@
           <t>df+3</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>Snap Kick</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>Snap Kick</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr">
+      <c r="I55" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
+      <c r="J55" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="J55" t="inlineStr">
+      <c r="K55" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="N55" t="inlineStr">
+      <c r="O55" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="O55" t="inlineStr">
+      <c r="P55" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="P55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>+1</t>
         </is>
       </c>
-      <c r="Q55" t="inlineStr">
+      <c r="R55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
+      <c r="T55" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="U55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr">
+      <c r="V55" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA55" t="inlineStr">
+      <c r="AB55" t="inlineStr">
         <is>
           <t>4d48b7fd-4056-4c92-9180-1a4e9610ea94</t>
         </is>
       </c>
-      <c r="AB55" t="inlineStr">
+      <c r="AC55" t="inlineStr">
         <is>
           <t>9c6dfeb8-cb03-4445-b170-8154a21206a4</t>
         </is>
@@ -5336,92 +5377,92 @@
           <t>uf+3+4</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>Earthquake Stomp</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>Earthquake Stomp</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="I56" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
+      <c r="J56" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="J56" t="inlineStr">
+      <c r="K56" t="inlineStr">
         <is>
           <t>47</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>-32</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
+      <c r="M56" t="inlineStr">
         <is>
           <t>-32</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr">
+      <c r="N56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N56" t="inlineStr">
+      <c r="O56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O56" t="inlineStr">
+      <c r="P56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q56" t="inlineStr">
+      <c r="R56" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="S56" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr">
+      <c r="T56" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="T56" t="inlineStr">
+      <c r="U56" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr">
+      <c r="V56" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="AA56" t="inlineStr">
+      <c r="AB56" t="inlineStr">
         <is>
           <t>6e849337-dc22-4ed2-8d38-77383ced35ba</t>
         </is>
       </c>
-      <c r="AB56" t="inlineStr">
+      <c r="AC56" t="inlineStr">
         <is>
           <t>f8ca735c-3855-47d4-a207-c88ef93a308e</t>
         </is>
@@ -5438,92 +5479,92 @@
           <t>FC+df+4 ,3</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>Bow &amp; Arrow</t>
         </is>
       </c>
-      <c r="H57" t="inlineStr">
+      <c r="I57" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I57" t="inlineStr">
+      <c r="J57" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="J57" t="inlineStr">
+      <c r="K57" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>-14 -15</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>-14 -15</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="N57" t="inlineStr">
+      <c r="O57" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="O57" t="inlineStr">
+      <c r="P57" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="P57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>-3 KD</t>
         </is>
       </c>
-      <c r="Q57" t="inlineStr">
+      <c r="R57" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="S57" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr">
+      <c r="T57" t="inlineStr">
         <is>
           <t>12,15</t>
         </is>
       </c>
-      <c r="T57" t="inlineStr">
+      <c r="U57" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr">
+      <c r="V57" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="AA57" t="inlineStr">
+      <c r="AB57" t="inlineStr">
         <is>
           <t>27e0d698-6a5c-45c2-a839-0317034200f6</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
+      <c r="AC57" t="inlineStr">
         <is>
           <t>f65d73c0-f50b-4969-b4f8-89a2bcf687e3</t>
         </is>
@@ -5540,92 +5581,92 @@
           <t>db+4</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
+      <c r="F58" t="inlineStr">
         <is>
           <t>Tiger Mountain</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="G58" t="inlineStr">
         <is>
           <t>Tiger Mountain</t>
         </is>
       </c>
-      <c r="H58" t="inlineStr">
+      <c r="I58" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
+      <c r="J58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J58" t="inlineStr">
+      <c r="K58" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K58" t="inlineStr">
+      <c r="L58" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="L58" t="inlineStr">
+      <c r="M58" t="inlineStr">
         <is>
           <t>-11</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr">
+      <c r="N58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="N58" t="inlineStr">
+      <c r="O58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="O58" t="inlineStr">
+      <c r="P58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="P58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="Q58" t="inlineStr">
+      <c r="R58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="S58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr">
+      <c r="T58" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T58" t="inlineStr">
+      <c r="U58" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr">
+      <c r="V58" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AA58" t="inlineStr">
+      <c r="AB58" t="inlineStr">
         <is>
           <t>55ac43c8-2020-4e4c-9657-d8a8512f58f4</t>
         </is>
       </c>
-      <c r="AB58" t="inlineStr">
+      <c r="AC58" t="inlineStr">
         <is>
           <t>f5e83266-a7a0-4a98-81dc-2db1fa94998e</t>
         </is>
@@ -5642,102 +5683,102 @@
           <t>db+4 ,2</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
+      <c r="F59" t="inlineStr">
         <is>
           <t>– False Lift</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="G59" t="inlineStr">
         <is>
           <t>Tiger Mountain – False Lift</t>
         </is>
       </c>
-      <c r="H59" t="inlineStr">
+      <c r="I59" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J59" t="inlineStr">
+      <c r="K59" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr">
+      <c r="L59" t="inlineStr">
         <is>
           <t>-13</t>
         </is>
       </c>
-      <c r="L59" t="inlineStr">
+      <c r="M59" t="inlineStr">
         <is>
           <t>-11 -13</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr">
+      <c r="N59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N59" t="inlineStr">
+      <c r="O59" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="O59" t="inlineStr">
+      <c r="P59" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>0 KD</t>
         </is>
       </c>
-      <c r="Q59" t="inlineStr">
+      <c r="R59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="S59" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr">
+      <c r="T59" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="T59" t="inlineStr">
+      <c r="U59" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr">
+      <c r="V59" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
+      <c r="Y59" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
+      <c r="AA59" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA59" t="inlineStr">
+      <c r="AB59" t="inlineStr">
         <is>
           <t>f53c4913-c634-4637-bd7d-ebd00f8f44c7</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
+      <c r="AC59" t="inlineStr">
         <is>
           <t>be3f5ece-450c-4186-9d54-7870dc3842d6</t>
         </is>
       </c>
-      <c r="AC59" t="inlineStr">
+      <c r="AD59" t="inlineStr">
         <is>
           <t>55ac43c8-2020-4e4c-9657-d8a8512f58f4</t>
         </is>
@@ -5754,102 +5795,102 @@
           <t>f+4</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>Rising Heaven Kick</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="G60" t="inlineStr">
         <is>
           <t>Rising Heaven Kick</t>
         </is>
       </c>
-      <c r="H60" t="inlineStr">
+      <c r="I60" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I60" t="inlineStr">
+      <c r="J60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="K60" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="L60" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="N60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
+      <c r="O60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O60" t="inlineStr">
+      <c r="P60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
+      <c r="R60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
+      <c r="Y60" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
+      <c r="AA60" t="inlineStr">
         <is>
           <t>TRUE</t>
         </is>
       </c>
-      <c r="AA60" t="inlineStr">
+      <c r="AB60" t="inlineStr">
         <is>
           <t>72f7803c-df33-4388-812c-4ca41b8b4a57</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
+      <c r="AC60" t="inlineStr">
         <is>
           <t>d563f1e0-3837-4c1d-8c86-8eef31ecf343</t>
         </is>
@@ -5866,92 +5907,92 @@
           <t>d+4</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>Razor Sweep</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="G61" t="inlineStr">
         <is>
           <t>Razor Sweep</t>
         </is>
       </c>
-      <c r="H61" t="inlineStr">
+      <c r="I61" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I61" t="inlineStr">
+      <c r="J61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="J61" t="inlineStr">
+      <c r="K61" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K61" t="inlineStr">
+      <c r="L61" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
+      <c r="M61" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr">
+      <c r="N61" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="N61" t="inlineStr">
+      <c r="O61" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="O61" t="inlineStr">
+      <c r="P61" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="P61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>-10</t>
         </is>
       </c>
-      <c r="Q61" t="inlineStr">
+      <c r="R61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="S61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S61" t="inlineStr">
+      <c r="T61" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="T61" t="inlineStr">
+      <c r="U61" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U61" t="inlineStr">
+      <c r="V61" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="AA61" t="inlineStr">
+      <c r="AB61" t="inlineStr">
         <is>
           <t>8b6db3ef-47c7-4b19-8bc9-f8244baf8f22</t>
         </is>
       </c>
-      <c r="AB61" t="inlineStr">
+      <c r="AC61" t="inlineStr">
         <is>
           <t>ec9acf99-1a10-4eb1-8142-b667b14c696d</t>
         </is>
@@ -5968,92 +6009,92 @@
           <t>d+4 ,N+4</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>Razor Sweep – High Kick</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J62" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K62" t="inlineStr">
+      <c r="L62" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L62" t="inlineStr">
+      <c r="M62" t="inlineStr">
         <is>
           <t>-9 -14</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N62" t="inlineStr">
+      <c r="O62" t="inlineStr">
         <is>
           <t>-10 -3</t>
         </is>
       </c>
-      <c r="O62" t="inlineStr">
+      <c r="P62" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>-10 -3</t>
         </is>
       </c>
-      <c r="Q62" t="inlineStr">
+      <c r="R62" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="S62" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr">
+      <c r="T62" t="inlineStr">
         <is>
           <t>10,23</t>
         </is>
       </c>
-      <c r="T62" t="inlineStr">
+      <c r="U62" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr">
+      <c r="V62" t="inlineStr">
         <is>
           <t>Lh</t>
         </is>
       </c>
-      <c r="AA62" t="inlineStr">
+      <c r="AB62" t="inlineStr">
         <is>
           <t>ef487d01-71fc-4098-899a-6b0cb078c8de</t>
         </is>
       </c>
-      <c r="AB62" t="inlineStr">
+      <c r="AC62" t="inlineStr">
         <is>
           <t>56b4cdc9-3730-47f8-a9a0-331e5049577a</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
+      <c r="AD62" t="inlineStr">
         <is>
           <t>8b6db3ef-47c7-4b19-8bc9-f8244baf8f22</t>
         </is>
@@ -6070,92 +6111,102 @@
           <t>d+4 ,db+4</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>d+4; df+4</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
+          <t>d+4,d+4; d+4,df+4</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="G63" t="inlineStr">
         <is>
           <t>Razor Sweep – Low Kick</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="I63" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="L63" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>-9 -19</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="N63" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="O63" t="inlineStr">
         <is>
           <t>-10 -8</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr">
+      <c r="P63" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="P63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>-10 -8</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
+      <c r="R63" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>10,10</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>LL</t>
         </is>
       </c>
-      <c r="AA63" t="inlineStr">
+      <c r="AB63" t="inlineStr">
         <is>
           <t>e4cdc703-4381-4e58-89fe-d5bfee442ab8</t>
         </is>
       </c>
-      <c r="AB63" t="inlineStr">
+      <c r="AC63" t="inlineStr">
         <is>
           <t>3cc451c2-8441-48b2-b3da-d1c546642309</t>
         </is>
       </c>
-      <c r="AC63" t="inlineStr">
+      <c r="AD63" t="inlineStr">
         <is>
           <t>8b6db3ef-47c7-4b19-8bc9-f8244baf8f22</t>
         </is>
@@ -6172,97 +6223,97 @@
           <t>d+4 ,1</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="F64" t="inlineStr">
         <is>
           <t>– Razor Edge</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="G64" t="inlineStr">
         <is>
           <t>Razor Sweep – Razor Edge</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
+      <c r="I64" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="J64" t="inlineStr">
+      <c r="K64" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="K64" t="inlineStr">
+      <c r="L64" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr">
+      <c r="M64" t="inlineStr">
         <is>
           <t>-9 -17</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr">
+      <c r="N64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N64" t="inlineStr">
+      <c r="O64" t="inlineStr">
         <is>
           <t>-10 KD</t>
         </is>
       </c>
-      <c r="O64" t="inlineStr">
+      <c r="P64" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>-10 KD</t>
         </is>
       </c>
-      <c r="Q64" t="inlineStr">
+      <c r="R64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="S64" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S64" t="inlineStr">
+      <c r="T64" t="inlineStr">
         <is>
           <t>10,21</t>
         </is>
       </c>
-      <c r="T64" t="inlineStr">
+      <c r="U64" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U64" t="inlineStr">
+      <c r="V64" t="inlineStr">
         <is>
           <t>Lm</t>
         </is>
       </c>
-      <c r="X64" t="inlineStr">
+      <c r="Y64" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="AA64" t="inlineStr">
+      <c r="AB64" t="inlineStr">
         <is>
           <t>246ff2b4-473d-4bb1-a24a-ea197f48693a</t>
         </is>
       </c>
-      <c r="AB64" t="inlineStr">
+      <c r="AC64" t="inlineStr">
         <is>
           <t>4fb1345e-36c8-477e-8854-2d0420b62470</t>
         </is>
       </c>
-      <c r="AC64" t="inlineStr">
+      <c r="AD64" t="inlineStr">
         <is>
           <t>8b6db3ef-47c7-4b19-8bc9-f8244baf8f22</t>
         </is>
@@ -6279,92 +6330,92 @@
           <t>WS+4</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="F65" t="inlineStr">
         <is>
           <t>Skyscraper Kick</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="G65" t="inlineStr">
         <is>
           <t>Skyscraper Kick</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr">
+      <c r="I65" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr">
+      <c r="J65" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="J65" t="inlineStr">
+      <c r="K65" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr">
+      <c r="L65" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
+      <c r="M65" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr">
+      <c r="N65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N65" t="inlineStr">
+      <c r="O65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O65" t="inlineStr">
+      <c r="P65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q65" t="inlineStr">
+      <c r="R65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="S65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S65" t="inlineStr">
+      <c r="T65" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="T65" t="inlineStr">
+      <c r="U65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U65" t="inlineStr">
+      <c r="V65" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="AA65" t="inlineStr">
+      <c r="AB65" t="inlineStr">
         <is>
           <t>84030389-43d0-4d46-9a9b-1e19e47b71e0</t>
         </is>
       </c>
-      <c r="AB65" t="inlineStr">
+      <c r="AC65" t="inlineStr">
         <is>
           <t>35858774-c1e9-442e-8942-420a84b9e890</t>
         </is>
@@ -6381,97 +6432,97 @@
           <t>4 ,4</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="F66" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="G66" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
+      <c r="I66" t="inlineStr">
         <is>
           <t>1 1</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
+      <c r="J66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="J66" t="inlineStr">
+      <c r="K66" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K66" t="inlineStr">
+      <c r="L66" t="inlineStr">
         <is>
           <t>-7 -7</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
+      <c r="M66" t="inlineStr">
         <is>
           <t>-7 -7</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr">
+      <c r="N66" t="inlineStr">
         <is>
           <t>-7 +4</t>
         </is>
       </c>
-      <c r="N66" t="inlineStr">
+      <c r="O66" t="inlineStr">
         <is>
           <t>-7 +4</t>
         </is>
       </c>
-      <c r="O66" t="inlineStr">
+      <c r="P66" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="P66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>KD +4</t>
         </is>
       </c>
-      <c r="Q66" t="inlineStr">
+      <c r="R66" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="S66" t="inlineStr">
         <is>
           <t>32</t>
         </is>
       </c>
-      <c r="S66" t="inlineStr">
+      <c r="T66" t="inlineStr">
         <is>
           <t>20,12</t>
         </is>
       </c>
-      <c r="T66" t="inlineStr">
+      <c r="U66" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="U66" t="inlineStr">
+      <c r="V66" t="inlineStr">
         <is>
           <t>hL</t>
         </is>
       </c>
-      <c r="X66" t="inlineStr">
+      <c r="Y66" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="AA66" t="inlineStr">
+      <c r="AB66" t="inlineStr">
         <is>
           <t>5aab2a17-826f-42bd-94b8-08931808f3b5</t>
         </is>
       </c>
-      <c r="AB66" t="inlineStr">
+      <c r="AC66" t="inlineStr">
         <is>
           <t>92e5e2e4-083c-4d18-a13e-73fdd43ab6e5</t>
         </is>
@@ -6488,92 +6539,92 @@
           <t>4 ,4 ,4</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
+      <c r="F67" t="inlineStr">
         <is>
           <t>– High Kick</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="G67" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – High Kick</t>
         </is>
       </c>
-      <c r="H67" t="inlineStr">
+      <c r="I67" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J67" t="inlineStr">
+      <c r="K67" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr">
+      <c r="L67" t="inlineStr">
         <is>
           <t>-14</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
+      <c r="M67" t="inlineStr">
         <is>
           <t>-7 -7 -14</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr">
+      <c r="N67" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="N67" t="inlineStr">
+      <c r="O67" t="inlineStr">
         <is>
           <t>-7 +4 -3</t>
         </is>
       </c>
-      <c r="O67" t="inlineStr">
+      <c r="P67" t="inlineStr">
         <is>
           <t>-3</t>
         </is>
       </c>
-      <c r="P67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>KD +4 -3</t>
         </is>
       </c>
-      <c r="Q67" t="inlineStr">
+      <c r="R67" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="S67" t="inlineStr">
         <is>
           <t>21</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr">
+      <c r="T67" t="inlineStr">
         <is>
           <t>20,12,21</t>
         </is>
       </c>
-      <c r="T67" t="inlineStr">
+      <c r="U67" t="inlineStr">
         <is>
           <t>h</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr">
+      <c r="V67" t="inlineStr">
         <is>
           <t>hLh</t>
         </is>
       </c>
-      <c r="AA67" t="inlineStr">
+      <c r="AB67" t="inlineStr">
         <is>
           <t>a1177aa0-5af9-41c9-9d20-b604e2a368c4</t>
         </is>
       </c>
-      <c r="AB67" t="inlineStr">
+      <c r="AC67" t="inlineStr">
         <is>
           <t>d0223606-0bb1-4b1e-baa0-fbe9b1c52a7e</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
+      <c r="AD67" t="inlineStr">
         <is>
           <t>5aab2a17-826f-42bd-94b8-08931808f3b5</t>
         </is>
@@ -6590,97 +6641,107 @@
           <t>4 ,4 ,db+4</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>d+4; df+4</t>
+        </is>
+      </c>
       <c r="E68" t="inlineStr">
         <is>
+          <t>4,4,d+4; 4,4,df+4</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
           <t>– Low Kick</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="G68" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – Low Kick</t>
         </is>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="I68" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J68" t="inlineStr">
+      <c r="K68" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr">
+      <c r="L68" t="inlineStr">
         <is>
           <t>-19</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
+      <c r="M68" t="inlineStr">
         <is>
           <t>-7 -7 -19</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr">
+      <c r="N68" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="N68" t="inlineStr">
+      <c r="O68" t="inlineStr">
         <is>
           <t>-7 +4 -8</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
+      <c r="P68" t="inlineStr">
         <is>
           <t>-8</t>
         </is>
       </c>
-      <c r="P68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>KD +4 -8</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="R68" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="S68" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr">
+      <c r="T68" t="inlineStr">
         <is>
           <t>20,12,20</t>
         </is>
       </c>
-      <c r="T68" t="inlineStr">
+      <c r="U68" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr">
+      <c r="V68" t="inlineStr">
         <is>
           <t>hLL</t>
         </is>
       </c>
-      <c r="X68" t="inlineStr">
+      <c r="Y68" t="inlineStr">
         <is>
           <t>RC</t>
         </is>
       </c>
-      <c r="AA68" t="inlineStr">
+      <c r="AB68" t="inlineStr">
         <is>
           <t>045fb669-6bb1-4bc4-9522-9e157b8d29c2</t>
         </is>
       </c>
-      <c r="AB68" t="inlineStr">
+      <c r="AC68" t="inlineStr">
         <is>
           <t>f5decfc4-0b87-4c2e-bc02-3c45532fb70c</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
+      <c r="AD68" t="inlineStr">
         <is>
           <t>5aab2a17-826f-42bd-94b8-08931808f3b5</t>
         </is>
@@ -6697,97 +6758,97 @@
           <t>4 ,4 ,1</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
+      <c r="F69" t="inlineStr">
         <is>
           <t>– Razor Edge</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="G69" t="inlineStr">
         <is>
           <t>Spinning Razor Kicks – Razor Edge</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="I69" t="inlineStr">
         <is>
           <t>1 1 1</t>
         </is>
       </c>
-      <c r="J69" t="inlineStr">
+      <c r="K69" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="K69" t="inlineStr">
+      <c r="L69" t="inlineStr">
         <is>
           <t>-17</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="M69" t="inlineStr">
         <is>
           <t>-7 -7 -17</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr">
+      <c r="N69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N69" t="inlineStr">
+      <c r="O69" t="inlineStr">
         <is>
           <t>-7 +4 KD</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
+      <c r="P69" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P69" t="inlineStr">
+      <c r="Q69" t="inlineStr">
         <is>
           <t>KD +4 KD</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="R69" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="S69" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="S69" t="inlineStr">
+      <c r="T69" t="inlineStr">
         <is>
           <t>20,12,23</t>
         </is>
       </c>
-      <c r="T69" t="inlineStr">
+      <c r="U69" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="U69" t="inlineStr">
+      <c r="V69" t="inlineStr">
         <is>
           <t>hLm</t>
         </is>
       </c>
-      <c r="X69" t="inlineStr">
+      <c r="Y69" t="inlineStr">
         <is>
           <t>JG</t>
         </is>
       </c>
-      <c r="AA69" t="inlineStr">
+      <c r="AB69" t="inlineStr">
         <is>
           <t>5db64110-1f4d-4f90-9391-a91ed8f9d3e5</t>
         </is>
       </c>
-      <c r="AB69" t="inlineStr">
+      <c r="AC69" t="inlineStr">
         <is>
           <t>5fc5bd4c-63ba-47b6-a6b5-e499a52925ec</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
+      <c r="AD69" t="inlineStr">
         <is>
           <t>5aab2a17-826f-42bd-94b8-08931808f3b5</t>
         </is>
@@ -6804,97 +6865,97 @@
           <t>SS+4</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
+      <c r="F70" t="inlineStr">
         <is>
           <t>Parting Sweep</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="G70" t="inlineStr">
         <is>
           <t>Parting Sweep</t>
         </is>
       </c>
-      <c r="H70" t="inlineStr">
+      <c r="I70" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
+      <c r="J70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="J70" t="inlineStr">
+      <c r="K70" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="K70" t="inlineStr">
+      <c r="L70" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
+      <c r="M70" t="inlineStr">
         <is>
           <t>-20</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr">
+      <c r="N70" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="N70" t="inlineStr">
+      <c r="O70" t="inlineStr">
         <is>
           <t>-9</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
+      <c r="P70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="R70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="S70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="S70" t="inlineStr">
+      <c r="T70" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="T70" t="inlineStr">
+      <c r="U70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="U70" t="inlineStr">
+      <c r="V70" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="X70" t="inlineStr">
+      <c r="Y70" t="inlineStr">
         <is>
           <t>PLDc</t>
         </is>
       </c>
-      <c r="AA70" t="inlineStr">
+      <c r="AB70" t="inlineStr">
         <is>
           <t>8a9778be-8808-4a8f-bbdf-4fbc4c9c190d</t>
         </is>
       </c>
-      <c r="AB70" t="inlineStr">
+      <c r="AC70" t="inlineStr">
         <is>
           <t>29f9df46-fa0c-480b-9614-468c20bee05d</t>
         </is>
@@ -6918,50 +6979,55 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
+          <t>b+2+4</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
           <t>High &amp; Mid Attack Reversal</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="G71" t="inlineStr">
         <is>
           <t>High &amp; Mid Attack Reversal</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="I71" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="R71" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="S71" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="S71" t="inlineStr">
+      <c r="T71" t="inlineStr">
         <is>
           <t>varies</t>
         </is>
       </c>
-      <c r="T71" t="inlineStr">
+      <c r="U71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U71" t="inlineStr">
+      <c r="V71" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="AA71" t="inlineStr">
+      <c r="AB71" t="inlineStr">
         <is>
           <t>c717c5d8-bf44-4e31-8794-568c3bcbe614</t>
         </is>
       </c>
-      <c r="AB71" t="inlineStr">
+      <c r="AC71" t="inlineStr">
         <is>
           <t>ddfd0912-0ab7-4281-89e8-163814e82e51</t>
         </is>
@@ -6998,130 +7064,135 @@
       </c>
       <c r="E74" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F74" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F74" s="1" t="inlineStr">
+      <c r="G74" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G74" s="1" t="inlineStr">
+      <c r="H74" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H74" s="1" t="inlineStr">
+      <c r="I74" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I74" s="1" t="inlineStr">
+      <c r="J74" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J74" s="1" t="inlineStr">
+      <c r="K74" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K74" s="1" t="inlineStr">
+      <c r="L74" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L74" s="1" t="inlineStr">
+      <c r="M74" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M74" s="1" t="inlineStr">
+      <c r="N74" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N74" s="1" t="inlineStr">
+      <c r="O74" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O74" s="1" t="inlineStr">
+      <c r="P74" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P74" s="1" t="inlineStr">
+      <c r="Q74" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q74" s="1" t="inlineStr">
+      <c r="R74" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R74" s="1" t="inlineStr">
+      <c r="S74" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S74" s="1" t="inlineStr">
+      <c r="T74" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T74" s="1" t="inlineStr">
+      <c r="U74" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U74" s="1" t="inlineStr">
+      <c r="V74" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V74" s="1" t="inlineStr">
+      <c r="W74" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W74" s="1" t="inlineStr">
+      <c r="X74" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X74" s="1" t="inlineStr">
+      <c r="Y74" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y74" s="1" t="inlineStr">
+      <c r="Z74" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z74" s="1" t="inlineStr">
+      <c r="AA74" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA74" s="1" t="inlineStr">
+      <c r="AB74" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB74" s="1" t="inlineStr">
+      <c r="AC74" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC74" s="1" t="inlineStr">
+      <c r="AD74" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD74" s="1" t="inlineStr">
+      <c r="AE74" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7138,82 +7209,82 @@
           <t>b,b+1</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
+      <c r="F75" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="G75" t="inlineStr">
         <is>
           <t>Heaven Cannon</t>
         </is>
       </c>
-      <c r="H75" t="inlineStr">
+      <c r="I75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
+      <c r="J75" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="J75" t="inlineStr">
+      <c r="K75" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr">
+      <c r="N75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N75" t="inlineStr">
+      <c r="O75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
+      <c r="P75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="R75" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="S75" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="S75" t="inlineStr">
+      <c r="T75" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="T75" t="inlineStr">
+      <c r="U75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U75" t="inlineStr">
+      <c r="V75" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA75" t="inlineStr">
+      <c r="AB75" t="inlineStr">
         <is>
           <t>9c67a8d1-e1ce-4704-a516-f651bcf3ec68</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
+      <c r="AC75" t="inlineStr">
         <is>
           <t>e3259208-bf5d-4bed-a249-6b714d1b1b2d</t>
         </is>
@@ -7230,72 +7301,72 @@
           <t>b,b+1~B</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
+      <c r="F76" t="inlineStr">
         <is>
           <t>– Cancel</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="G76" t="inlineStr">
         <is>
           <t>Heaven Cannon – Cancel</t>
         </is>
       </c>
-      <c r="H76" t="inlineStr">
+      <c r="I76" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>60</t>
         </is>
       </c>
-      <c r="N76" t="inlineStr">
+      <c r="O76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q76" t="inlineStr">
+      <c r="R76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="S76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="S76" t="inlineStr">
+      <c r="T76" t="inlineStr">
         <is>
           <t>70,-</t>
         </is>
       </c>
-      <c r="T76" t="inlineStr">
+      <c r="U76" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="U76" t="inlineStr">
+      <c r="V76" t="inlineStr">
         <is>
           <t>1-</t>
         </is>
       </c>
-      <c r="AA76" t="inlineStr">
+      <c r="AB76" t="inlineStr">
         <is>
           <t>3b795eb4-5397-474c-b01b-6ba07d9bf8fe</t>
         </is>
       </c>
-      <c r="AB76" t="inlineStr">
+      <c r="AC76" t="inlineStr">
         <is>
           <t>9ab99b53-5522-4753-a615-674674c60ac0</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
+      <c r="AD76" t="inlineStr">
         <is>
           <t>9c67a8d1-e1ce-4704-a516-f651bcf3ec68</t>
         </is>
@@ -7312,82 +7383,82 @@
           <t>b+1+2</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Indigo Punch</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Indigo Punch</t>
         </is>
       </c>
-      <c r="H77" t="inlineStr">
+      <c r="I77" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I77" t="inlineStr">
+      <c r="J77" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="J77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>73</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr">
+      <c r="N77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="N77" t="inlineStr">
+      <c r="O77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="O77" t="inlineStr">
+      <c r="P77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="P77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>KD</t>
         </is>
       </c>
-      <c r="Q77" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="S77" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="S77" t="inlineStr">
+      <c r="T77" t="inlineStr">
         <is>
           <t>100</t>
         </is>
       </c>
-      <c r="T77" t="inlineStr">
+      <c r="U77" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="U77" t="inlineStr">
+      <c r="V77" t="inlineStr">
         <is>
           <t>!</t>
         </is>
       </c>
-      <c r="AA77" t="inlineStr">
+      <c r="AB77" t="inlineStr">
         <is>
           <t>1a35b41c-2a5d-47f7-96bd-d3f8d982cdab</t>
         </is>
       </c>
-      <c r="AB77" t="inlineStr">
+      <c r="AC77" t="inlineStr">
         <is>
           <t>5bb4f9ad-c514-48d3-b6ab-b51b602d6f1c</t>
         </is>
@@ -7424,130 +7495,135 @@
       </c>
       <c r="E80" s="1" t="inlineStr">
         <is>
+          <t>Alt Commands Full</t>
+        </is>
+      </c>
+      <c r="F80" s="1" t="inlineStr">
+        <is>
           <t>Move Name</t>
         </is>
       </c>
-      <c r="F80" s="1" t="inlineStr">
+      <c r="G80" s="1" t="inlineStr">
         <is>
           <t>Move Name Full</t>
         </is>
       </c>
-      <c r="G80" s="1" t="inlineStr">
+      <c r="H80" s="1" t="inlineStr">
         <is>
           <t>To Stance</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
+      <c r="I80" s="1" t="inlineStr">
         <is>
           <t>Hits Per Move</t>
         </is>
       </c>
-      <c r="I80" s="1" t="inlineStr">
+      <c r="J80" s="1" t="inlineStr">
         <is>
           <t>Speed</t>
         </is>
       </c>
-      <c r="J80" s="1" t="inlineStr">
+      <c r="K80" s="1" t="inlineStr">
         <is>
           <t>Speed Full</t>
         </is>
       </c>
-      <c r="K80" s="1" t="inlineStr">
+      <c r="L80" s="1" t="inlineStr">
         <is>
           <t>Block Adv</t>
         </is>
       </c>
-      <c r="L80" s="1" t="inlineStr">
+      <c r="M80" s="1" t="inlineStr">
         <is>
           <t>Block Adv Full</t>
         </is>
       </c>
-      <c r="M80" s="1" t="inlineStr">
+      <c r="N80" s="1" t="inlineStr">
         <is>
           <t>Hit Adv</t>
         </is>
       </c>
-      <c r="N80" s="1" t="inlineStr">
+      <c r="O80" s="1" t="inlineStr">
         <is>
           <t>Hit Adv Full</t>
         </is>
       </c>
-      <c r="O80" s="1" t="inlineStr">
+      <c r="P80" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv</t>
         </is>
       </c>
-      <c r="P80" s="1" t="inlineStr">
+      <c r="Q80" s="1" t="inlineStr">
         <is>
           <t>Counter Hit Adv Full</t>
         </is>
       </c>
-      <c r="Q80" s="1" t="inlineStr">
+      <c r="R80" s="1" t="inlineStr">
         <is>
           <t>Damage</t>
         </is>
       </c>
-      <c r="R80" s="1" t="inlineStr">
+      <c r="S80" s="1" t="inlineStr">
         <is>
           <t>Damage Sum</t>
         </is>
       </c>
-      <c r="S80" s="1" t="inlineStr">
+      <c r="T80" s="1" t="inlineStr">
         <is>
           <t>Damage Full</t>
         </is>
       </c>
-      <c r="T80" s="1" t="inlineStr">
+      <c r="U80" s="1" t="inlineStr">
         <is>
           <t>Hit Range</t>
         </is>
       </c>
-      <c r="U80" s="1" t="inlineStr">
+      <c r="V80" s="1" t="inlineStr">
         <is>
           <t>Hit Range Full</t>
         </is>
       </c>
-      <c r="V80" s="1" t="inlineStr">
+      <c r="W80" s="1" t="inlineStr">
         <is>
           <t>Throw Type</t>
         </is>
       </c>
-      <c r="W80" s="1" t="inlineStr">
+      <c r="X80" s="1" t="inlineStr">
         <is>
           <t>Throw Escape</t>
         </is>
       </c>
-      <c r="X80" s="1" t="inlineStr">
+      <c r="Y80" s="1" t="inlineStr">
         <is>
           <t>Properties</t>
         </is>
       </c>
-      <c r="Y80" s="1" t="inlineStr">
+      <c r="Z80" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="Z80" s="1" t="inlineStr">
+      <c r="AA80" s="1" t="inlineStr">
         <is>
           <t>Taggable</t>
         </is>
       </c>
-      <c r="AA80" s="1" t="inlineStr">
+      <c r="AB80" s="1" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
-      <c r="AB80" s="1" t="inlineStr">
+      <c r="AC80" s="1" t="inlineStr">
         <is>
           <t>ML UUID</t>
         </is>
       </c>
-      <c r="AC80" s="1" t="inlineStr">
+      <c r="AD80" s="1" t="inlineStr">
         <is>
           <t>Parent UUID</t>
         </is>
       </c>
-      <c r="AD80" s="1" t="inlineStr">
+      <c r="AE80" s="1" t="inlineStr">
         <is>
           <t>Unmatched</t>
         </is>
@@ -7564,47 +7640,47 @@
           <t>2 ,1 ,1 ,2 ,3 ,3 ,3 ,4 ,4 ,1</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
+      <c r="I81" t="inlineStr">
         <is>
           <t>1 1 1 1 1 1 1 1 1 1</t>
         </is>
       </c>
-      <c r="Q81" t="inlineStr">
+      <c r="R81" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
-      <c r="R81" t="inlineStr">
+      <c r="S81" t="inlineStr">
         <is>
           <t>84</t>
         </is>
       </c>
-      <c r="S81" t="inlineStr">
+      <c r="T81" t="inlineStr">
         <is>
           <t>8,6,6,6,6,6,6,7,8,25</t>
         </is>
       </c>
-      <c r="T81" t="inlineStr">
+      <c r="U81" t="inlineStr">
         <is>
           <t>hmmhlmhhLm</t>
         </is>
       </c>
-      <c r="U81" t="inlineStr">
+      <c r="V81" t="inlineStr">
         <is>
           <t>hmmhlmhhLm</t>
         </is>
       </c>
-      <c r="AA81" t="inlineStr">
+      <c r="AB81" t="inlineStr">
         <is>
           <t>f2b1b105-8e73-4505-9cf6-fc48f600c675</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
+      <c r="AC81" t="inlineStr">
         <is>
           <t>f2b1b105-8e73-4505-9cf6-fc48f600c675</t>
         </is>
       </c>
-      <c r="AD81" t="inlineStr">
+      <c r="AE81" t="inlineStr">
         <is>
           <t>ML only</t>
         </is>
